--- a/All_Code/Q2_yy/Results/Tables/annual_cost_summary.xlsx
+++ b/All_Code/Q2_yy/Results/Tables/annual_cost_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="annual" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13951370.95426664</v>
+        <v>13885012.62256014</v>
       </c>
       <c r="C2" t="n">
-        <v>41770.57171936121</v>
+        <v>41571.89407952138</v>
       </c>
       <c r="D2" t="n">
         <v>334</v>
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>682383.6983927872</v>
+        <v>823950.8718955689</v>
       </c>
       <c r="C3" t="n">
-        <v>2043.064965247866</v>
+        <v>2466.918778130446</v>
       </c>
       <c r="D3" t="n">
         <v>334</v>
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14633754.65265943</v>
+        <v>14708963.49445571</v>
       </c>
       <c r="C4" t="n">
-        <v>43813.63668460907</v>
+        <v>44038.81285765184</v>
       </c>
       <c r="D4" t="n">
         <v>334</v>
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14637011.73570099</v>
+        <v>14708963.49445571</v>
       </c>
       <c r="C5" t="n">
-        <v>43823.38843024247</v>
+        <v>44038.81285765184</v>
       </c>
       <c r="D5" t="n">
         <v>334</v>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7552.443450228718</v>
+        <v>6000.000000000028</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1426.268450435303</v>
+        <v>6000</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161057.5382380272</v>
+        <v>217628.3542411625</v>
       </c>
       <c r="C8" t="n">
-        <v>482.2081983174468</v>
+        <v>651.5818989256361</v>
       </c>
       <c r="D8" t="n">
         <v>334</v>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1650078.432281699</v>
+        <v>1979772.819081801</v>
       </c>
       <c r="C9" t="n">
-        <v>4940.354587669757</v>
+        <v>5927.463530185031</v>
       </c>
       <c r="D9" t="n">
         <v>334</v>
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1873770.15524894</v>
+        <v>1535001.652922041</v>
       </c>
       <c r="C10" t="n">
-        <v>5610.090285176469</v>
+        <v>4595.81333210192</v>
       </c>
       <c r="D10" t="n">
         <v>334</v>
@@ -593,7 +593,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>参数: beta=0.2, M=30, kappa2=0.132917, alpha=0.9；费用不含 eps 与 kappa2 罚项</t>
+          <t>参数: beta=0.2, M=30, kappa2=0.531667, alpha=0.9；费用不含 eps 与 kappa2 罚项</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
